--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_diff.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/X9.cis.beta.carotene/Resultats_X9.cis.beta.carotene_moy_diff.xlsx
@@ -1,205 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\U108-N806\Documents\STAGE_M2_ROSA_NIRS\VitaSPEC\vitaspec_R\ROSA_vitaSPEC\Results\test_pretraitements\X9.cis.beta.carotene\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="58">
-  <si>
-    <t>Pretraitement</t>
-  </si>
-  <si>
-    <t>LV1_diff</t>
-  </si>
-  <si>
-    <t>LV2_diff</t>
-  </si>
-  <si>
-    <t>LV3_diff</t>
-  </si>
-  <si>
-    <t>LV4_diff</t>
-  </si>
-  <si>
-    <t>LV5_diff</t>
-  </si>
-  <si>
-    <t>LV6_diff</t>
-  </si>
-  <si>
-    <t>LV7_diff</t>
-  </si>
-  <si>
-    <t>LV8_diff</t>
-  </si>
-  <si>
-    <t>LV9_diff</t>
-  </si>
-  <si>
-    <t>LV10_diff</t>
-  </si>
-  <si>
-    <t>LV11_diff</t>
-  </si>
-  <si>
-    <t>LV12_diff</t>
-  </si>
-  <si>
-    <t>LV13_diff</t>
-  </si>
-  <si>
-    <t>LV14_diff</t>
-  </si>
-  <si>
-    <t>LV15_diff</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1000,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
-  </si>
-  <si>
-    <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(1,3,5)_</t>
-  </si>
-  <si>
-    <t>adj_snv_sder_c(2,3,15)_</t>
-  </si>
-  <si>
-    <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -245,52 +61,13 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="3">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -332,7 +109,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -364,10 +141,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -399,7 +175,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -575,2173 +350,2408 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:P43"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="51.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="16" width="12" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:Q43"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:16" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>16</v>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Pretraitement</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>LV0_diff</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>LV1_diff</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>LV2_diff</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>LV3_diff</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>LV4_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>LV5_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>LV6_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>LV7_diff</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>LV8_diff</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>LV9_diff</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>LV10_diff</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>LV11_diff</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>LV12_diff</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>LV13_diff</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>LV14_diff</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>LV15_diff</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1000,1)_snv_</t>
+        </is>
       </c>
       <c r="B2">
-        <v>3.7113717745297703E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C2">
-        <v>5.7799545459113089E-2</v>
+        <v>0.03711371772113337</v>
       </c>
       <c r="D2">
-        <v>8.1317052878041973E-2</v>
+        <v>0.05779954540290916</v>
       </c>
       <c r="E2">
-        <v>8.3466621273078911E-2</v>
+        <v>0.08131705250690907</v>
       </c>
       <c r="F2">
-        <v>0.110633689642212</v>
+        <v>0.08346662091410972</v>
       </c>
       <c r="G2">
-        <v>0.11736271883718</v>
+        <v>0.1106336891573453</v>
       </c>
       <c r="H2">
-        <v>0.13070443905420229</v>
+        <v>0.117362718615633</v>
       </c>
       <c r="I2">
-        <v>0.14125272071878031</v>
+        <v>0.1307044396942358</v>
       </c>
       <c r="J2">
-        <v>0.1401096121794814</v>
+        <v>0.1412527213401424</v>
       </c>
       <c r="K2">
-        <v>0.15777807345330311</v>
+        <v>0.140109613212605</v>
       </c>
       <c r="L2">
-        <v>0.18588568060319829</v>
+        <v>0.1577780744197598</v>
       </c>
       <c r="M2">
-        <v>0.23491993120911711</v>
+        <v>0.1858856810189277</v>
       </c>
       <c r="N2">
-        <v>0.327897250386251</v>
+        <v>0.2349199307701124</v>
       </c>
       <c r="O2">
-        <v>0.43916057459414282</v>
+        <v>0.3278972500309204</v>
       </c>
       <c r="P2">
-        <v>0.47381638396022008</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>17</v>
+        <v>0.4391605771551825</v>
+      </c>
+      <c r="Q2">
+        <v>0.4738163868377829</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1200,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B3">
-        <v>4.2677620296663943E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C3">
-        <v>4.3143789168492652E-2</v>
+        <v>0.042677619881206</v>
       </c>
       <c r="D3">
-        <v>8.0140550623583606E-2</v>
+        <v>0.04314378900387661</v>
       </c>
       <c r="E3">
-        <v>0.17626897162658969</v>
+        <v>0.08014055112549101</v>
       </c>
       <c r="F3">
-        <v>0.1931320323008599</v>
+        <v>0.1762689715272769</v>
       </c>
       <c r="G3">
-        <v>0.22248022843251611</v>
+        <v>0.19313202843191</v>
       </c>
       <c r="H3">
-        <v>0.25691783763173559</v>
+        <v>0.2224802261906318</v>
       </c>
       <c r="I3">
-        <v>0.29295237791588158</v>
+        <v>0.2569178402528906</v>
       </c>
       <c r="J3">
-        <v>0.34057626320005591</v>
+        <v>0.2929523840914866</v>
       </c>
       <c r="K3">
-        <v>0.40286115506590497</v>
+        <v>0.340576263973688</v>
       </c>
       <c r="L3">
-        <v>0.47139420195726423</v>
+        <v>0.4028611526853186</v>
       </c>
       <c r="M3">
-        <v>0.53106024321133072</v>
+        <v>0.4713942159746828</v>
       </c>
       <c r="N3">
-        <v>0.58593364889621236</v>
+        <v>0.5310602411849574</v>
       </c>
       <c r="O3">
-        <v>0.61426474050444591</v>
+        <v>0.5859336755532297</v>
       </c>
       <c r="P3">
-        <v>0.61319103169019473</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>18</v>
+        <v>0.6142647677437425</v>
+      </c>
+      <c r="Q3">
+        <v>0.613191058807361</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B4">
-        <v>3.7156490888305527E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C4">
-        <v>5.6702933994972733E-2</v>
+        <v>0.03715649086396172</v>
       </c>
       <c r="D4">
-        <v>6.9232894585019578E-2</v>
+        <v>0.05670293395724713</v>
       </c>
       <c r="E4">
-        <v>0.1271705113946287</v>
+        <v>0.0692328943469232</v>
       </c>
       <c r="F4">
-        <v>0.13493063628684829</v>
+        <v>0.1271705113249629</v>
       </c>
       <c r="G4">
-        <v>0.11628269054015029</v>
+        <v>0.1349306364581226</v>
       </c>
       <c r="H4">
-        <v>0.12633485287868729</v>
+        <v>0.1162826912702642</v>
       </c>
       <c r="I4">
-        <v>0.1406129797166322</v>
+        <v>0.1263348523274951</v>
       </c>
       <c r="J4">
-        <v>0.20563662151889839</v>
+        <v>0.140612979333741</v>
       </c>
       <c r="K4">
-        <v>0.26517624388955219</v>
+        <v>0.2056366207909053</v>
       </c>
       <c r="L4">
-        <v>0.30089129969874839</v>
+        <v>0.2651762420520822</v>
       </c>
       <c r="M4">
-        <v>0.39380631100257552</v>
+        <v>0.3008912967410515</v>
       </c>
       <c r="N4">
-        <v>0.47590589462261751</v>
+        <v>0.3938063084411758</v>
       </c>
       <c r="O4">
-        <v>0.53526814304770132</v>
+        <v>0.4759058911573547</v>
       </c>
       <c r="P4">
-        <v>0.58552862890217772</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>19</v>
+        <v>0.5352681438077476</v>
+      </c>
+      <c r="Q4">
+        <v>0.5855286370063513</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B5">
-        <v>3.1631847143537888E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C5">
-        <v>8.2222511121640862E-2</v>
+        <v>0.03163184714218442</v>
       </c>
       <c r="D5">
-        <v>0.12451360432753911</v>
+        <v>0.08222251070121406</v>
       </c>
       <c r="E5">
-        <v>0.15209256877757241</v>
+        <v>0.124513600992725</v>
       </c>
       <c r="F5">
-        <v>0.17293620462588319</v>
+        <v>0.1520925692444023</v>
       </c>
       <c r="G5">
-        <v>0.1811212020188436</v>
+        <v>0.1729362041143968</v>
       </c>
       <c r="H5">
-        <v>0.1940708212703455</v>
+        <v>0.1811212036498533</v>
       </c>
       <c r="I5">
-        <v>0.22395447185443901</v>
+        <v>0.1940708213959494</v>
       </c>
       <c r="J5">
-        <v>0.29526133762123452</v>
+        <v>0.2239544736901535</v>
       </c>
       <c r="K5">
-        <v>0.36216963931465468</v>
+        <v>0.2952613315720938</v>
       </c>
       <c r="L5">
-        <v>0.41136418610579728</v>
+        <v>0.36216964733505</v>
       </c>
       <c r="M5">
-        <v>0.44121628397653467</v>
+        <v>0.4113642048791382</v>
       </c>
       <c r="N5">
-        <v>0.44889621294315452</v>
+        <v>0.4412163156639214</v>
       </c>
       <c r="O5">
-        <v>0.47555366661825088</v>
+        <v>0.4488962516462219</v>
       </c>
       <c r="P5">
-        <v>0.50283569867928091</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>20</v>
+        <v>0.475553720409346</v>
+      </c>
+      <c r="Q5">
+        <v>0.5028357730937293</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_msc_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B6">
-        <v>2.890541683351194E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C6">
-        <v>7.2192129079884537E-2</v>
+        <v>0.02890541683217912</v>
       </c>
       <c r="D6">
-        <v>0.10990318846442609</v>
+        <v>0.07219212905386729</v>
       </c>
       <c r="E6">
-        <v>0.13059081298949979</v>
+        <v>0.109903186540143</v>
       </c>
       <c r="F6">
-        <v>0.1324662737192247</v>
+        <v>0.1305908139752323</v>
       </c>
       <c r="G6">
-        <v>0.16676727237234359</v>
+        <v>0.1324662734416845</v>
       </c>
       <c r="H6">
-        <v>0.1700371832540872</v>
+        <v>0.1667672778896322</v>
       </c>
       <c r="I6">
-        <v>0.21776772497439051</v>
+        <v>0.17003718629079</v>
       </c>
       <c r="J6">
-        <v>0.28441119336644782</v>
+        <v>0.217767735053267</v>
       </c>
       <c r="K6">
-        <v>0.30781540817475678</v>
+        <v>0.2844112011662726</v>
       </c>
       <c r="L6">
-        <v>0.35917652373157127</v>
+        <v>0.3078154250442507</v>
       </c>
       <c r="M6">
-        <v>0.39537293632819859</v>
+        <v>0.3591765468307545</v>
       </c>
       <c r="N6">
-        <v>0.43964342700363951</v>
+        <v>0.3953729666052669</v>
       </c>
       <c r="O6">
-        <v>0.46359941987243558</v>
+        <v>0.4396434887078169</v>
       </c>
       <c r="P6">
-        <v>0.50707066094043296</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>21</v>
+        <v>0.4635995072906955</v>
+      </c>
+      <c r="Q6">
+        <v>0.5070707791173211</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B7">
-        <v>3.6432264636905132E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C7">
-        <v>5.4084389521506897E-2</v>
+        <v>0.03643226460663856</v>
       </c>
       <c r="D7">
-        <v>8.3537477191074516E-2</v>
+        <v>0.05408438946064564</v>
       </c>
       <c r="E7">
-        <v>7.8641151368945228E-2</v>
+        <v>0.08353747656562738</v>
       </c>
       <c r="F7">
-        <v>9.7430273023103475E-2</v>
+        <v>0.07864115086126233</v>
       </c>
       <c r="G7">
-        <v>9.5875421759333612E-2</v>
+        <v>0.09743027286855699</v>
       </c>
       <c r="H7">
-        <v>0.1191306823644053</v>
+        <v>0.09587542214424871</v>
       </c>
       <c r="I7">
-        <v>0.1242964930380497</v>
+        <v>0.119130683332096</v>
       </c>
       <c r="J7">
-        <v>0.14211152145019909</v>
+        <v>0.1242964942017701</v>
       </c>
       <c r="K7">
-        <v>0.19844609897775911</v>
+        <v>0.1421115236323274</v>
       </c>
       <c r="L7">
-        <v>0.24213745838026629</v>
+        <v>0.1984460983067353</v>
       </c>
       <c r="M7">
-        <v>0.26978492521630282</v>
+        <v>0.2421374544269219</v>
       </c>
       <c r="N7">
-        <v>0.35828029120161842</v>
+        <v>0.2697849228302516</v>
       </c>
       <c r="O7">
-        <v>0.44604644810356081</v>
+        <v>0.3582802956623313</v>
       </c>
       <c r="P7">
-        <v>0.50584199862954393</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>22</v>
+        <v>0.4460464582806685</v>
+      </c>
+      <c r="Q7">
+        <v>0.5058420245300839</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B8">
-        <v>3.309564975098378E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C8">
-        <v>5.1618044582608602E-2</v>
+        <v>0.03309564976460894</v>
       </c>
       <c r="D8">
-        <v>8.4415064065691769E-2</v>
+        <v>0.05161804458202129</v>
       </c>
       <c r="E8">
-        <v>9.5654176148654013E-2</v>
+        <v>0.0844150637930311</v>
       </c>
       <c r="F8">
-        <v>0.1045968234136658</v>
+        <v>0.09565417600677661</v>
       </c>
       <c r="G8">
-        <v>0.13840545510510699</v>
+        <v>0.104596823499947</v>
       </c>
       <c r="H8">
-        <v>0.14440131665355471</v>
+        <v>0.1384054564972409</v>
       </c>
       <c r="I8">
-        <v>0.17087312097165841</v>
+        <v>0.144401317370431</v>
       </c>
       <c r="J8">
-        <v>0.2297822698854978</v>
+        <v>0.1708731231181493</v>
       </c>
       <c r="K8">
-        <v>0.31379431050006601</v>
+        <v>0.2297822749398621</v>
       </c>
       <c r="L8">
-        <v>0.3589370078723701</v>
+        <v>0.3137943110236222</v>
       </c>
       <c r="M8">
-        <v>0.40204839949758148</v>
+        <v>0.3589370137948059</v>
       </c>
       <c r="N8">
-        <v>0.48403174205232452</v>
+        <v>0.4020484118022482</v>
       </c>
       <c r="O8">
-        <v>0.55048233333661978</v>
+        <v>0.4840317564874624</v>
       </c>
       <c r="P8">
-        <v>0.62988529435063878</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>23</v>
+        <v>0.550482341154158</v>
+      </c>
+      <c r="Q8">
+        <v>0.6298852945608979</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B9">
-        <v>3.3033451525491753E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C9">
-        <v>4.9090799437173933E-2</v>
+        <v>0.03303345153726656</v>
       </c>
       <c r="D9">
-        <v>8.0861881684199388E-2</v>
+        <v>0.04909079942501887</v>
       </c>
       <c r="E9">
-        <v>9.100890390341021E-2</v>
+        <v>0.0808618813624683</v>
       </c>
       <c r="F9">
-        <v>9.9900002435763025E-2</v>
+        <v>0.09100890383216897</v>
       </c>
       <c r="G9">
-        <v>0.12878867859244381</v>
+        <v>0.09990000232474239</v>
       </c>
       <c r="H9">
-        <v>0.12732843796998539</v>
+        <v>0.1287886798523231</v>
       </c>
       <c r="I9">
-        <v>0.14209780694887231</v>
+        <v>0.1273284382568943</v>
       </c>
       <c r="J9">
-        <v>0.1588566938233785</v>
+        <v>0.1420978078994048</v>
       </c>
       <c r="K9">
-        <v>0.19845267735415101</v>
+        <v>0.1588566951126532</v>
       </c>
       <c r="L9">
-        <v>0.2347790415154748</v>
+        <v>0.1984526761555322</v>
       </c>
       <c r="M9">
-        <v>0.27210820042876038</v>
+        <v>0.2347790470520135</v>
       </c>
       <c r="N9">
-        <v>0.32718220249743352</v>
+        <v>0.2721082203319299</v>
       </c>
       <c r="O9">
-        <v>0.35289270000501188</v>
+        <v>0.3271822386009285</v>
       </c>
       <c r="P9">
-        <v>0.3773703506907885</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>24</v>
+        <v>0.3528927419923034</v>
+      </c>
+      <c r="Q9">
+        <v>0.3773703951729299</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B10">
-        <v>3.045777259126237E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C10">
-        <v>4.8104484073793967E-2</v>
+        <v>0.03045777260607591</v>
       </c>
       <c r="D10">
-        <v>8.4067969286155342E-2</v>
+        <v>0.04810448406706663</v>
       </c>
       <c r="E10">
-        <v>9.4585847552270397E-2</v>
+        <v>0.084067969012114</v>
       </c>
       <c r="F10">
-        <v>0.1032035480965785</v>
+        <v>0.09458584752539201</v>
       </c>
       <c r="G10">
-        <v>0.1311574736051172</v>
+        <v>0.1032035480874368</v>
       </c>
       <c r="H10">
-        <v>0.12651206723614691</v>
+        <v>0.1311574752434231</v>
       </c>
       <c r="I10">
-        <v>0.14278347383856879</v>
+        <v>0.126512068058528</v>
       </c>
       <c r="J10">
-        <v>0.15877284842597669</v>
+        <v>0.1427834750289411</v>
       </c>
       <c r="K10">
-        <v>0.19609535869809841</v>
+        <v>0.1587728470430593</v>
       </c>
       <c r="L10">
-        <v>0.23046199984494259</v>
+        <v>0.1960953597085525</v>
       </c>
       <c r="M10">
-        <v>0.26615677310180341</v>
+        <v>0.2304620052031698</v>
       </c>
       <c r="N10">
-        <v>0.31094750227401191</v>
+        <v>0.2661567922858794</v>
       </c>
       <c r="O10">
-        <v>0.33477386663099062</v>
+        <v>0.3109475340706996</v>
       </c>
       <c r="P10">
-        <v>0.36643183281510272</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>25</v>
+        <v>0.3347739037125386</v>
+      </c>
+      <c r="Q10">
+        <v>0.3664318813169534</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B11">
-        <v>3.450866779059969E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C11">
-        <v>5.0619192354169007E-2</v>
+        <v>0.03450866780955564</v>
       </c>
       <c r="D11">
-        <v>8.6005419891240442E-2</v>
+        <v>0.05061919235140938</v>
       </c>
       <c r="E11">
-        <v>9.6300073751265258E-2</v>
+        <v>0.08600541964984521</v>
       </c>
       <c r="F11">
-        <v>0.10388526291922941</v>
+        <v>0.09630007372014115</v>
       </c>
       <c r="G11">
-        <v>0.13148420552310561</v>
+        <v>0.1038852630508833</v>
       </c>
       <c r="H11">
-        <v>0.13107083976188369</v>
+        <v>0.1314842071609486</v>
       </c>
       <c r="I11">
-        <v>0.14519509693206889</v>
+        <v>0.1310708402899748</v>
       </c>
       <c r="J11">
-        <v>0.1628153542101376</v>
+        <v>0.1451950985534251</v>
       </c>
       <c r="K11">
-        <v>0.20611142147165101</v>
+        <v>0.1628153569766942</v>
       </c>
       <c r="L11">
-        <v>0.23662774893713079</v>
+        <v>0.2061114232752193</v>
       </c>
       <c r="M11">
-        <v>0.26950162850449672</v>
+        <v>0.2366277565946633</v>
       </c>
       <c r="N11">
-        <v>0.30880171866990819</v>
+        <v>0.2695016499461339</v>
       </c>
       <c r="O11">
-        <v>0.32230465327490232</v>
+        <v>0.3088017509807679</v>
       </c>
       <c r="P11">
-        <v>0.35591783692216478</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>26</v>
+        <v>0.3223046845182745</v>
+      </c>
+      <c r="Q11">
+        <v>0.3559178692573406</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B12">
-        <v>2.78996939965655E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C12">
-        <v>9.8286754210170191E-2</v>
+        <v>0.02789969398575809</v>
       </c>
       <c r="D12">
-        <v>0.11521903167894131</v>
+        <v>0.09828675256117059</v>
       </c>
       <c r="E12">
-        <v>0.1335653016349049</v>
+        <v>0.1152190285871232</v>
       </c>
       <c r="F12">
-        <v>0.14628889845184381</v>
+        <v>0.1335653016156063</v>
       </c>
       <c r="G12">
-        <v>0.15487516555537051</v>
+        <v>0.146288898822701</v>
       </c>
       <c r="H12">
-        <v>0.16457395976926331</v>
+        <v>0.1548751666054033</v>
       </c>
       <c r="I12">
-        <v>0.19855518382347279</v>
+        <v>0.164573958305596</v>
       </c>
       <c r="J12">
-        <v>0.24555067456252719</v>
+        <v>0.1985551806880969</v>
       </c>
       <c r="K12">
-        <v>0.32813796368981257</v>
+        <v>0.2455506744920535</v>
       </c>
       <c r="L12">
-        <v>0.38580230461605608</v>
+        <v>0.3281379749835887</v>
       </c>
       <c r="M12">
-        <v>0.44054412123995051</v>
+        <v>0.3858023131909892</v>
       </c>
       <c r="N12">
-        <v>0.45601083104527768</v>
+        <v>0.4405441305076308</v>
       </c>
       <c r="O12">
-        <v>0.50141992308030892</v>
+        <v>0.4560108439352104</v>
       </c>
       <c r="P12">
-        <v>0.56669186189669019</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>27</v>
+        <v>0.5014199482251648</v>
+      </c>
+      <c r="Q12">
+        <v>0.5666918924253779</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_detr_2_sder_c(1,3,9)_</t>
+        </is>
       </c>
       <c r="B13">
-        <v>2.986393664618819E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C13">
-        <v>0.13361826304278479</v>
+        <v>0.02986393669388093</v>
       </c>
       <c r="D13">
-        <v>0.1328441276887046</v>
+        <v>0.1336182632118794</v>
       </c>
       <c r="E13">
-        <v>0.17050534333459039</v>
+        <v>0.1328441266964258</v>
       </c>
       <c r="F13">
-        <v>0.23413527314983251</v>
+        <v>0.1705053435884143</v>
       </c>
       <c r="G13">
-        <v>0.2332273204731086</v>
+        <v>0.2341352840531711</v>
       </c>
       <c r="H13">
-        <v>0.23098937168845071</v>
+        <v>0.2332273309281522</v>
       </c>
       <c r="I13">
-        <v>0.25197911995369809</v>
+        <v>0.230989379628288</v>
       </c>
       <c r="J13">
-        <v>0.29977718403632497</v>
+        <v>0.2519791248749771</v>
       </c>
       <c r="K13">
-        <v>0.38531464318014241</v>
+        <v>0.2997771695931196</v>
       </c>
       <c r="L13">
-        <v>0.44350882063376651</v>
+        <v>0.3853146243675892</v>
       </c>
       <c r="M13">
-        <v>0.47064592156913521</v>
+        <v>0.4435087977369752</v>
       </c>
       <c r="N13">
-        <v>0.52288266537882921</v>
+        <v>0.4706459001161507</v>
       </c>
       <c r="O13">
-        <v>0.57063103123530579</v>
+        <v>0.5228826387457428</v>
       </c>
       <c r="P13">
-        <v>0.63293495597383387</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>28</v>
+        <v>0.5706309839038919</v>
+      </c>
+      <c r="Q13">
+        <v>0.6329348817984566</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B14">
-        <v>3.5553129382294817E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C14">
-        <v>5.2745770229467137E-2</v>
+        <v>0.03555312935831889</v>
       </c>
       <c r="D14">
-        <v>7.9951843919830345E-2</v>
+        <v>0.05274577017298532</v>
       </c>
       <c r="E14">
-        <v>7.7799038760906214E-2</v>
+        <v>0.07995184323963966</v>
       </c>
       <c r="F14">
-        <v>9.4287419430706509E-2</v>
+        <v>0.07779903824359757</v>
       </c>
       <c r="G14">
-        <v>9.0267492872347366E-2</v>
+        <v>0.09428741934601836</v>
       </c>
       <c r="H14">
-        <v>0.1115803129464619</v>
+        <v>0.09026749326958361</v>
       </c>
       <c r="I14">
-        <v>0.1140951559257187</v>
+        <v>0.1115803139239556</v>
       </c>
       <c r="J14">
-        <v>0.12650386870405911</v>
+        <v>0.114095156620548</v>
       </c>
       <c r="K14">
-        <v>0.1575711939780898</v>
+        <v>0.1265038698722698</v>
       </c>
       <c r="L14">
-        <v>0.1776114195179096</v>
+        <v>0.1575711941479137</v>
       </c>
       <c r="M14">
-        <v>0.1912584068271079</v>
+        <v>0.1776114171215005</v>
       </c>
       <c r="N14">
-        <v>0.25148302574402781</v>
+        <v>0.1912584069250038</v>
       </c>
       <c r="O14">
-        <v>0.2999102638840131</v>
+        <v>0.2514830386518898</v>
       </c>
       <c r="P14">
-        <v>0.33638725725534879</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>29</v>
+        <v>0.2999102778458333</v>
+      </c>
+      <c r="Q14">
+        <v>0.3363872697562531</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B15">
-        <v>3.5870791273118707E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C15">
-        <v>5.3636803047532489E-2</v>
+        <v>0.03587079124792514</v>
       </c>
       <c r="D15">
-        <v>8.1929676897593451E-2</v>
+        <v>0.05363680299665857</v>
       </c>
       <c r="E15">
-        <v>7.9876134848400615E-2</v>
+        <v>0.08192967625791514</v>
       </c>
       <c r="F15">
-        <v>9.5655709372115427E-2</v>
+        <v>0.07987613435709395</v>
       </c>
       <c r="G15">
-        <v>9.4739424157337604E-2</v>
+        <v>0.09565570928020117</v>
       </c>
       <c r="H15">
-        <v>0.1133624778843649</v>
+        <v>0.09473942458424389</v>
       </c>
       <c r="I15">
-        <v>0.1136214885957046</v>
+        <v>0.1133624787475254</v>
       </c>
       <c r="J15">
-        <v>0.1242448311103385</v>
+        <v>0.1136214898072746</v>
       </c>
       <c r="K15">
-        <v>0.15163370774873319</v>
+        <v>0.1242448329506365</v>
       </c>
       <c r="L15">
-        <v>0.16933183235344679</v>
+        <v>0.1516337084259108</v>
       </c>
       <c r="M15">
-        <v>0.18340863796008591</v>
+        <v>0.1693318312754545</v>
       </c>
       <c r="N15">
-        <v>0.26409982168869989</v>
+        <v>0.1834086390074612</v>
       </c>
       <c r="O15">
-        <v>0.3114803657777459</v>
+        <v>0.2640998341191984</v>
       </c>
       <c r="P15">
-        <v>0.31485588245857837</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>30</v>
+        <v>0.3114803782282855</v>
+      </c>
+      <c r="Q15">
+        <v>0.3148559020395779</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,25)_</t>
+        </is>
       </c>
       <c r="B16">
-        <v>3.2827066368366131E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C16">
-        <v>5.0223052844775851E-2</v>
+        <v>0.0328270663581019</v>
       </c>
       <c r="D16">
-        <v>7.8644178360723904E-2</v>
+        <v>0.05022305282526085</v>
       </c>
       <c r="E16">
-        <v>7.6953967576502302E-2</v>
+        <v>0.07864417774790944</v>
       </c>
       <c r="F16">
-        <v>9.121512520440278E-2</v>
+        <v>0.07695396713153368</v>
       </c>
       <c r="G16">
-        <v>8.7506307593042898E-2</v>
+        <v>0.09121512497153639</v>
       </c>
       <c r="H16">
-        <v>0.10586082900459</v>
+        <v>0.08750630785024871</v>
       </c>
       <c r="I16">
-        <v>0.1086590637141361</v>
+        <v>0.1058608295317366</v>
       </c>
       <c r="J16">
-        <v>0.11825900392691011</v>
+        <v>0.1086590654134061</v>
       </c>
       <c r="K16">
-        <v>0.14232105644566281</v>
+        <v>0.1182590068067433</v>
       </c>
       <c r="L16">
-        <v>0.15907697683152461</v>
+        <v>0.142321056610473</v>
       </c>
       <c r="M16">
-        <v>0.17371581124038249</v>
+        <v>0.1590769752160728</v>
       </c>
       <c r="N16">
-        <v>0.25926901860884671</v>
+        <v>0.1737158108153932</v>
       </c>
       <c r="O16">
-        <v>0.31248652772548002</v>
+        <v>0.259269031215932</v>
       </c>
       <c r="P16">
-        <v>0.31358889614034652</v>
-      </c>
-    </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>31</v>
+        <v>0.3124865397045157</v>
+      </c>
+      <c r="Q16">
+        <v>0.3135889088093192</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B17">
-        <v>3.2753652349903288E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C17">
-        <v>5.0769981463918153E-2</v>
+        <v>0.03275365232472438</v>
       </c>
       <c r="D17">
-        <v>7.5923699468326111E-2</v>
+        <v>0.05076998140312916</v>
       </c>
       <c r="E17">
-        <v>7.3891165581025819E-2</v>
+        <v>0.07592369891413087</v>
       </c>
       <c r="F17">
-        <v>9.0179045874790975E-2</v>
+        <v>0.0738911651549381</v>
       </c>
       <c r="G17">
-        <v>8.7958342205117224E-2</v>
+        <v>0.09017904576470215</v>
       </c>
       <c r="H17">
-        <v>0.10713611903788491</v>
+        <v>0.08795834249977574</v>
       </c>
       <c r="I17">
-        <v>0.1081902148758469</v>
+        <v>0.1071361197108399</v>
       </c>
       <c r="J17">
-        <v>0.1194599384634636</v>
+        <v>0.1081902154811274</v>
       </c>
       <c r="K17">
-        <v>0.1432406662373609</v>
+        <v>0.1194599392953221</v>
       </c>
       <c r="L17">
-        <v>0.15982102137691359</v>
+        <v>0.1432406663751938</v>
       </c>
       <c r="M17">
-        <v>0.17217229423527991</v>
+        <v>0.1598210198368689</v>
       </c>
       <c r="N17">
-        <v>0.24841056655438939</v>
+        <v>0.1721722946889513</v>
       </c>
       <c r="O17">
-        <v>0.30509851543507321</v>
+        <v>0.2484105796122642</v>
       </c>
       <c r="P17">
-        <v>0.30898333895195251</v>
-      </c>
-    </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>32</v>
+        <v>0.3050985281777502</v>
+      </c>
+      <c r="Q17">
+        <v>0.3089833540755389</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B18">
-        <v>3.0336569026109931E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C18">
-        <v>0.1095099220058259</v>
+        <v>0.03033656902713439</v>
       </c>
       <c r="D18">
-        <v>0.12325877181536909</v>
+        <v>0.1095099197154609</v>
       </c>
       <c r="E18">
-        <v>0.14686803337101459</v>
+        <v>0.1232587684715861</v>
       </c>
       <c r="F18">
-        <v>0.14916946504656539</v>
+        <v>0.1468680332939791</v>
       </c>
       <c r="G18">
-        <v>0.18557531505073749</v>
+        <v>0.1491694651712715</v>
       </c>
       <c r="H18">
-        <v>0.17680798862684879</v>
+        <v>0.1855753133353175</v>
       </c>
       <c r="I18">
-        <v>0.2032833063883718</v>
+        <v>0.1768079868770767</v>
       </c>
       <c r="J18">
-        <v>0.25015273180753972</v>
+        <v>0.203283303023827</v>
       </c>
       <c r="K18">
-        <v>0.32000845792850191</v>
+        <v>0.2501527433250623</v>
       </c>
       <c r="L18">
-        <v>0.36874854493275</v>
+        <v>0.3200084633439095</v>
       </c>
       <c r="M18">
-        <v>0.4035860239589889</v>
+        <v>0.3687485529902891</v>
       </c>
       <c r="N18">
-        <v>0.40162302862170202</v>
+        <v>0.4035860418996214</v>
       </c>
       <c r="O18">
-        <v>0.42528185571075189</v>
+        <v>0.4016230524068066</v>
       </c>
       <c r="P18">
-        <v>0.45809016385454432</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>33</v>
+        <v>0.4252818879060188</v>
+      </c>
+      <c r="Q18">
+        <v>0.4580901966497746</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,21)_</t>
+        </is>
       </c>
       <c r="B19">
-        <v>2.8970737065485311E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C19">
-        <v>0.10294892171350881</v>
+        <v>0.02897073707152792</v>
       </c>
       <c r="D19">
-        <v>0.11032487640194499</v>
+        <v>0.1029489212786344</v>
       </c>
       <c r="E19">
-        <v>0.1248293351624615</v>
+        <v>0.1103248746021235</v>
       </c>
       <c r="F19">
-        <v>0.1136722246791841</v>
+        <v>0.1248293360064747</v>
       </c>
       <c r="G19">
-        <v>0.15100708608540789</v>
+        <v>0.113672217442635</v>
       </c>
       <c r="H19">
-        <v>0.14988509318650489</v>
+        <v>0.1510070856813178</v>
       </c>
       <c r="I19">
-        <v>0.18641410348288201</v>
+        <v>0.1498850939418392</v>
       </c>
       <c r="J19">
-        <v>0.23916544366946299</v>
+        <v>0.1864141039349139</v>
       </c>
       <c r="K19">
-        <v>0.2660439629198339</v>
+        <v>0.2391654487467426</v>
       </c>
       <c r="L19">
-        <v>0.32535531509642818</v>
+        <v>0.2660439733883433</v>
       </c>
       <c r="M19">
-        <v>0.35044475413184378</v>
+        <v>0.3253553346220222</v>
       </c>
       <c r="N19">
-        <v>0.38722022599245792</v>
+        <v>0.3504447782111673</v>
       </c>
       <c r="O19">
-        <v>0.41604258409031353</v>
+        <v>0.3872202711072189</v>
       </c>
       <c r="P19">
-        <v>0.47201392060318859</v>
-      </c>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>34</v>
+        <v>0.4160426474286836</v>
+      </c>
+      <c r="Q19">
+        <v>0.4720140076959207</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B20">
-        <v>2.8413785465361659E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C20">
-        <v>8.6998353823042274E-2</v>
+        <v>0.02841378546398832</v>
       </c>
       <c r="D20">
-        <v>9.8875577210100984E-2</v>
+        <v>0.08699835420227059</v>
       </c>
       <c r="E20">
-        <v>0.1186234085776494</v>
+        <v>0.09887557670135461</v>
       </c>
       <c r="F20">
-        <v>0.1116226418764622</v>
+        <v>0.1186234092932038</v>
       </c>
       <c r="G20">
-        <v>0.12076514232656869</v>
+        <v>0.1116226423549461</v>
       </c>
       <c r="H20">
-        <v>0.13942791951965741</v>
+        <v>0.1207651429564006</v>
       </c>
       <c r="I20">
-        <v>0.17574463063684839</v>
+        <v>0.1394279262352592</v>
       </c>
       <c r="J20">
-        <v>0.21514225953277491</v>
+        <v>0.1757446308844394</v>
       </c>
       <c r="K20">
-        <v>0.24352703281597851</v>
+        <v>0.2151422656725424</v>
       </c>
       <c r="L20">
-        <v>0.28353530271551741</v>
+        <v>0.2435270492872963</v>
       </c>
       <c r="M20">
-        <v>0.30838929471540022</v>
+        <v>0.283535324539207</v>
       </c>
       <c r="N20">
-        <v>0.33098232813854461</v>
+        <v>0.3083893304240986</v>
       </c>
       <c r="O20">
-        <v>0.38006597852587792</v>
+        <v>0.330982370932656</v>
       </c>
       <c r="P20">
-        <v>0.44413823703681071</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>35</v>
+        <v>0.3800660422203239</v>
+      </c>
+      <c r="Q20">
+        <v>0.4441382495748173</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B21">
-        <v>3.7936931166678567E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C21">
-        <v>4.0803992721457127E-2</v>
+        <v>0.03793693081545868</v>
       </c>
       <c r="D21">
-        <v>7.1560568979368577E-2</v>
+        <v>0.04080399258743467</v>
       </c>
       <c r="E21">
-        <v>0.17761349139521759</v>
+        <v>0.07156056920121562</v>
       </c>
       <c r="F21">
-        <v>0.1561468082213899</v>
+        <v>0.177613494265926</v>
       </c>
       <c r="G21">
-        <v>0.19788613000857919</v>
+        <v>0.156146808171387</v>
       </c>
       <c r="H21">
-        <v>0.30563740578045667</v>
+        <v>0.1978861360502803</v>
       </c>
       <c r="I21">
-        <v>0.35991714107382999</v>
+        <v>0.3056373993736122</v>
       </c>
       <c r="J21">
-        <v>0.39323369772343192</v>
+        <v>0.3599171721373526</v>
       </c>
       <c r="K21">
-        <v>0.44991113748621309</v>
+        <v>0.3932337276349111</v>
       </c>
       <c r="L21">
-        <v>0.50457408539890136</v>
+        <v>0.4499111445324437</v>
       </c>
       <c r="M21">
-        <v>0.53507786066356433</v>
+        <v>0.5045741296148885</v>
       </c>
       <c r="N21">
-        <v>0.5648817194986302</v>
+        <v>0.5350778979179001</v>
       </c>
       <c r="O21">
-        <v>0.58221980765181269</v>
+        <v>0.5648817614318222</v>
       </c>
       <c r="P21">
-        <v>0.61109571032181664</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>36</v>
+        <v>0.5822198486974292</v>
+      </c>
+      <c r="Q21">
+        <v>0.61109576081873</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>adj_red_c(1,1400,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B22">
-        <v>4.5149744853845257E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C22">
-        <v>4.1822133483327813E-2</v>
+        <v>0.04514974440468383</v>
       </c>
       <c r="D22">
-        <v>7.1221172801209764E-2</v>
+        <v>0.04182213348501257</v>
       </c>
       <c r="E22">
-        <v>0.19000670877694589</v>
+        <v>0.07122117263982414</v>
       </c>
       <c r="F22">
-        <v>0.1568934202179203</v>
+        <v>0.1900067133464403</v>
       </c>
       <c r="G22">
-        <v>0.18710802860308609</v>
+        <v>0.156893421054231</v>
       </c>
       <c r="H22">
-        <v>0.29173518839796803</v>
+        <v>0.1871080256372959</v>
       </c>
       <c r="I22">
-        <v>0.3509436093800668</v>
+        <v>0.2917351889981377</v>
       </c>
       <c r="J22">
-        <v>0.41945229522668692</v>
+        <v>0.350943652589855</v>
       </c>
       <c r="K22">
-        <v>0.44641836759529541</v>
+        <v>0.4194523472377464</v>
       </c>
       <c r="L22">
-        <v>0.50341681323574805</v>
+        <v>0.446418443945225</v>
       </c>
       <c r="M22">
-        <v>0.54320113689045069</v>
+        <v>0.5034169114863891</v>
       </c>
       <c r="N22">
-        <v>0.5536896667886384</v>
+        <v>0.5432012613133832</v>
       </c>
       <c r="O22">
-        <v>0.56609020852791825</v>
+        <v>0.5536898149042728</v>
       </c>
       <c r="P22">
-        <v>0.61681475045954692</v>
-      </c>
-    </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>37</v>
+        <v>0.5660903830124695</v>
+      </c>
+      <c r="Q22">
+        <v>0.6168149621652974</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>adj_red_c(40,1300,1)_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B23">
-        <v>2.898345365394411E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C23">
-        <v>4.4065843975964247E-2</v>
+        <v>0.02898345360336096</v>
       </c>
       <c r="D23">
-        <v>9.2246568057160916E-2</v>
+        <v>0.04406584345165859</v>
       </c>
       <c r="E23">
-        <v>9.3900157343097979E-2</v>
+        <v>0.0922465813087805</v>
       </c>
       <c r="F23">
-        <v>0.2101004004518025</v>
+        <v>0.09390016009821694</v>
       </c>
       <c r="G23">
-        <v>0.2427469158245428</v>
+        <v>0.2101003802256656</v>
       </c>
       <c r="H23">
-        <v>0.35527927741342769</v>
+        <v>0.2427468880083466</v>
       </c>
       <c r="I23">
-        <v>0.42293227192842481</v>
+        <v>0.3552792473265196</v>
       </c>
       <c r="J23">
-        <v>0.44950544861303399</v>
+        <v>0.4229322770564273</v>
       </c>
       <c r="K23">
-        <v>0.50383867753390699</v>
+        <v>0.4495054742341976</v>
       </c>
       <c r="L23">
-        <v>0.57903605986981455</v>
+        <v>0.5038387404019702</v>
       </c>
       <c r="M23">
-        <v>0.6489700119158256</v>
+        <v>0.5790362106415988</v>
       </c>
       <c r="N23">
-        <v>0.70915338404899142</v>
+        <v>0.64897021911653</v>
       </c>
       <c r="O23">
-        <v>0.72925940646389087</v>
+        <v>0.7091536296877439</v>
       </c>
       <c r="P23">
-        <v>0.79001243076792882</v>
-      </c>
-    </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>38</v>
+        <v>0.7292596912869654</v>
+      </c>
+      <c r="Q23">
+        <v>0.790012886778952</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_msc_</t>
+        </is>
       </c>
       <c r="B24">
-        <v>2.81830793101745E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C24">
-        <v>4.6106462681803073E-2</v>
+        <v>0.02818307929689667</v>
       </c>
       <c r="D24">
-        <v>8.6506738515882309E-2</v>
+        <v>0.04610646262846529</v>
       </c>
       <c r="E24">
-        <v>8.5819398551050363E-2</v>
+        <v>0.08650673739976689</v>
       </c>
       <c r="F24">
-        <v>0.1038449141088208</v>
+        <v>0.08581939766916102</v>
       </c>
       <c r="G24">
-        <v>0.101951618458844</v>
+        <v>0.1038449134836177</v>
       </c>
       <c r="H24">
-        <v>0.1222874986219228</v>
+        <v>0.1019516181929729</v>
       </c>
       <c r="I24">
-        <v>0.14668442199663351</v>
+        <v>0.1222874983257797</v>
       </c>
       <c r="J24">
-        <v>0.18996344368488399</v>
+        <v>0.1466844244621776</v>
       </c>
       <c r="K24">
-        <v>0.25052069616515099</v>
+        <v>0.1899634520943612</v>
       </c>
       <c r="L24">
-        <v>0.32130447904722059</v>
+        <v>0.2505207279644196</v>
       </c>
       <c r="M24">
-        <v>0.43001467719563219</v>
+        <v>0.3213045047095184</v>
       </c>
       <c r="N24">
-        <v>0.4749981164057635</v>
+        <v>0.4300146876440797</v>
       </c>
       <c r="O24">
-        <v>0.52838993627825848</v>
+        <v>0.4749980908178417</v>
       </c>
       <c r="P24">
-        <v>0.57424494179609975</v>
-      </c>
-    </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>39</v>
+        <v>0.5283898859820959</v>
+      </c>
+      <c r="Q24">
+        <v>0.5742448976995962</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_</t>
+        </is>
       </c>
       <c r="B25">
-        <v>2.5249193007567779E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C25">
-        <v>4.4423771234235583E-2</v>
+        <v>0.02524919299931538</v>
       </c>
       <c r="D25">
-        <v>9.0735552519235485E-2</v>
+        <v>0.04442377119684227</v>
       </c>
       <c r="E25">
-        <v>8.5930812636035303E-2</v>
+        <v>0.09073555149873636</v>
       </c>
       <c r="F25">
-        <v>0.1124854535257853</v>
+        <v>0.08593081226095811</v>
       </c>
       <c r="G25">
-        <v>0.1175054304208648</v>
+        <v>0.1124854525302499</v>
       </c>
       <c r="H25">
-        <v>0.13533973040443029</v>
+        <v>0.1175054295879345</v>
       </c>
       <c r="I25">
-        <v>0.18856751620933079</v>
+        <v>0.1353397302407947</v>
       </c>
       <c r="J25">
-        <v>0.17817191252365891</v>
+        <v>0.1885675157966608</v>
       </c>
       <c r="K25">
-        <v>0.22133449818300621</v>
+        <v>0.1781719185210761</v>
       </c>
       <c r="L25">
-        <v>0.29034512908158011</v>
+        <v>0.2213345195015297</v>
       </c>
       <c r="M25">
-        <v>0.33369577532392508</v>
+        <v>0.290345165663906</v>
       </c>
       <c r="N25">
-        <v>0.42987695446607083</v>
+        <v>0.3336957668355214</v>
       </c>
       <c r="O25">
-        <v>0.47198132754174449</v>
+        <v>0.4298769158829485</v>
       </c>
       <c r="P25">
-        <v>0.51055988955477982</v>
-      </c>
-    </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>40</v>
+        <v>0.471981258633261</v>
+      </c>
+      <c r="Q25">
+        <v>0.5105597932624023</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_</t>
+        </is>
       </c>
       <c r="B26">
-        <v>2.6970685049099611E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C26">
-        <v>4.8534588963266352E-2</v>
+        <v>0.02697068503979672</v>
       </c>
       <c r="D26">
-        <v>0.11569400053800361</v>
+        <v>0.0485345888273786</v>
       </c>
       <c r="E26">
-        <v>9.6670425771907098E-2</v>
+        <v>0.1156939998632018</v>
       </c>
       <c r="F26">
-        <v>0.1168253695988621</v>
+        <v>0.09667042562544392</v>
       </c>
       <c r="G26">
-        <v>0.1066844311311245</v>
+        <v>0.1168253686306059</v>
       </c>
       <c r="H26">
-        <v>0.1148507662203589</v>
+        <v>0.1066844308462844</v>
       </c>
       <c r="I26">
-        <v>0.14567587713592561</v>
+        <v>0.1148507666091734</v>
       </c>
       <c r="J26">
-        <v>0.2229421710837132</v>
+        <v>0.1456758766517385</v>
       </c>
       <c r="K26">
-        <v>0.26815422004865103</v>
+        <v>0.2229421916948158</v>
       </c>
       <c r="L26">
-        <v>0.34674837775976991</v>
+        <v>0.2681542216100997</v>
       </c>
       <c r="M26">
-        <v>0.42495116839360703</v>
+        <v>0.3467483572034457</v>
       </c>
       <c r="N26">
-        <v>0.45422762453350318</v>
+        <v>0.4249511111154245</v>
       </c>
       <c r="O26">
-        <v>0.510737587363159</v>
+        <v>0.4542275368557825</v>
       </c>
       <c r="P26">
-        <v>0.5598010716652364</v>
-      </c>
-    </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>41</v>
+        <v>0.5107374774940596</v>
+      </c>
+      <c r="Q26">
+        <v>0.5598009305699763</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_detr_2_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B27">
-        <v>2.5155635671524901E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C27">
-        <v>4.6225230055635953E-2</v>
+        <v>0.02515563566566803</v>
       </c>
       <c r="D27">
-        <v>0.1122910520841999</v>
+        <v>0.04622522992141154</v>
       </c>
       <c r="E27">
-        <v>9.0890449124327866E-2</v>
+        <v>0.1122910514142544</v>
       </c>
       <c r="F27">
-        <v>0.11359768459250261</v>
+        <v>0.09089044877473107</v>
       </c>
       <c r="G27">
-        <v>9.9294360138136306E-2</v>
+        <v>0.1135976835686193</v>
       </c>
       <c r="H27">
-        <v>0.10259048222277201</v>
+        <v>0.099294360321454</v>
       </c>
       <c r="I27">
-        <v>0.1165954988606662</v>
+        <v>0.1025904824740504</v>
       </c>
       <c r="J27">
-        <v>0.15275719469227489</v>
+        <v>0.1165954977372112</v>
       </c>
       <c r="K27">
-        <v>0.1636407974810731</v>
+        <v>0.1527572028415121</v>
       </c>
       <c r="L27">
-        <v>0.18934022375227549</v>
+        <v>0.1636408026015911</v>
       </c>
       <c r="M27">
-        <v>0.25810523585363437</v>
+        <v>0.1893402244967842</v>
       </c>
       <c r="N27">
-        <v>0.27336334242982269</v>
+        <v>0.2581052299336196</v>
       </c>
       <c r="O27">
-        <v>0.31341593140952367</v>
+        <v>0.2733633231530532</v>
       </c>
       <c r="P27">
-        <v>0.33977646269755651</v>
-      </c>
-    </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>42</v>
+        <v>0.3134159023592017</v>
+      </c>
+      <c r="Q27">
+        <v>0.3397764348886346</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,21)_</t>
+        </is>
       </c>
       <c r="B28">
-        <v>2.454469045521079E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C28">
-        <v>4.1612411880071143E-2</v>
+        <v>0.02454469044962915</v>
       </c>
       <c r="D28">
-        <v>8.9967211713680606E-2</v>
+        <v>0.04161241184155273</v>
       </c>
       <c r="E28">
-        <v>8.4492678088170292E-2</v>
+        <v>0.08996721069364977</v>
       </c>
       <c r="F28">
-        <v>0.10559411792721821</v>
+        <v>0.08449267760769674</v>
       </c>
       <c r="G28">
-        <v>0.1055521919800594</v>
+        <v>0.1055941183876559</v>
       </c>
       <c r="H28">
-        <v>0.1175700382263157</v>
+        <v>0.1055521911298627</v>
       </c>
       <c r="I28">
-        <v>0.14776175820179219</v>
+        <v>0.1175700374540073</v>
       </c>
       <c r="J28">
-        <v>0.13199190284275811</v>
+        <v>0.1477617636261281</v>
       </c>
       <c r="K28">
-        <v>0.14436150721801561</v>
+        <v>0.1319919052091744</v>
       </c>
       <c r="L28">
-        <v>0.17235627850649421</v>
+        <v>0.1443615134947788</v>
       </c>
       <c r="M28">
-        <v>0.18299113231808831</v>
+        <v>0.1723562945250009</v>
       </c>
       <c r="N28">
-        <v>0.2209521844388429</v>
+        <v>0.1829911362031055</v>
       </c>
       <c r="O28">
-        <v>0.24409611597811301</v>
+        <v>0.2209521925200909</v>
       </c>
       <c r="P28">
-        <v>0.30744553725149532</v>
-      </c>
-    </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>43</v>
+        <v>0.2440961077309699</v>
+      </c>
+      <c r="Q28">
+        <v>0.3074454978607717</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,25)_</t>
+        </is>
       </c>
       <c r="B29">
-        <v>2.6593569202518989E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C29">
-        <v>4.4319643840832423E-2</v>
+        <v>0.02659356919473166</v>
       </c>
       <c r="D29">
-        <v>8.9983640223392336E-2</v>
+        <v>0.04431964379626008</v>
       </c>
       <c r="E29">
-        <v>8.6937488880439728E-2</v>
+        <v>0.08998363916333074</v>
       </c>
       <c r="F29">
-        <v>0.1104398337722228</v>
+        <v>0.08693748816028923</v>
       </c>
       <c r="G29">
-        <v>0.11121643148370799</v>
+        <v>0.1104398324691287</v>
       </c>
       <c r="H29">
-        <v>0.12436550770928589</v>
+        <v>0.1112164306282929</v>
       </c>
       <c r="I29">
-        <v>0.15128142427258931</v>
+        <v>0.1243655072578684</v>
       </c>
       <c r="J29">
-        <v>0.13820709767607781</v>
+        <v>0.1512814297476579</v>
       </c>
       <c r="K29">
-        <v>0.14599172529457341</v>
+        <v>0.1382071410243971</v>
       </c>
       <c r="L29">
-        <v>0.17210844712169759</v>
+        <v>0.1459917347280564</v>
       </c>
       <c r="M29">
-        <v>0.181045448647738</v>
+        <v>0.1721084474744974</v>
       </c>
       <c r="N29">
-        <v>0.21092337808855191</v>
+        <v>0.1810454356125613</v>
       </c>
       <c r="O29">
-        <v>0.22727643774886661</v>
+        <v>0.2109233830436257</v>
       </c>
       <c r="P29">
-        <v>0.28424305633630842</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>44</v>
+        <v>0.2272764312429911</v>
+      </c>
+      <c r="Q29">
+        <v>0.2842429804681557</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,27)_</t>
+        </is>
       </c>
       <c r="B30">
-        <v>2.5866336241035959E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C30">
-        <v>4.342022951704505E-2</v>
+        <v>0.02586633623500567</v>
       </c>
       <c r="D30">
-        <v>8.7354665805358556E-2</v>
+        <v>0.04342022947254187</v>
       </c>
       <c r="E30">
-        <v>8.3855643374616484E-2</v>
+        <v>0.08735466483563459</v>
       </c>
       <c r="F30">
-        <v>0.10783679263960071</v>
+        <v>0.08385564283876623</v>
       </c>
       <c r="G30">
-        <v>0.1085298406810985</v>
+        <v>0.107836791882469</v>
       </c>
       <c r="H30">
-        <v>0.1235399814433138</v>
+        <v>0.1085298397774399</v>
       </c>
       <c r="I30">
-        <v>0.15028358485342641</v>
+        <v>0.1235399805828146</v>
       </c>
       <c r="J30">
-        <v>0.13797467689434459</v>
+        <v>0.1502835823206921</v>
       </c>
       <c r="K30">
-        <v>0.1415586477146116</v>
+        <v>0.1379746778482591</v>
       </c>
       <c r="L30">
-        <v>0.16995431166546551</v>
+        <v>0.1415586527210462</v>
       </c>
       <c r="M30">
-        <v>0.1777355295390676</v>
+        <v>0.1699543234026859</v>
       </c>
       <c r="N30">
-        <v>0.20407853902827941</v>
+        <v>0.1777355353798811</v>
       </c>
       <c r="O30">
-        <v>0.21809335558017651</v>
+        <v>0.2040785410483497</v>
       </c>
       <c r="P30">
-        <v>0.27240551549730913</v>
-      </c>
-    </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>45</v>
+        <v>0.2180933333863236</v>
+      </c>
+      <c r="Q30">
+        <v>0.2724054712543235</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,2,31)_</t>
+        </is>
       </c>
       <c r="B31">
-        <v>2.706670091448116E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C31">
-        <v>4.5657890617050827E-2</v>
+        <v>0.02706670090972785</v>
       </c>
       <c r="D31">
-        <v>9.1804513190871573E-2</v>
+        <v>0.04565789058354031</v>
       </c>
       <c r="E31">
-        <v>8.6474099369967083E-2</v>
+        <v>0.09180451226266773</v>
       </c>
       <c r="F31">
-        <v>0.1083789766618363</v>
+        <v>0.08647409885674473</v>
       </c>
       <c r="G31">
-        <v>0.1102124533851879</v>
+        <v>0.1083789756375104</v>
       </c>
       <c r="H31">
-        <v>0.1229900944630555</v>
+        <v>0.1102124524622009</v>
       </c>
       <c r="I31">
-        <v>0.14857383360082091</v>
+        <v>0.1229900940234272</v>
       </c>
       <c r="J31">
-        <v>0.13927566569408881</v>
+        <v>0.1485738365759934</v>
       </c>
       <c r="K31">
-        <v>0.14107712249029891</v>
+        <v>0.1392756667916443</v>
       </c>
       <c r="L31">
-        <v>0.16645902994505321</v>
+        <v>0.141077127846956</v>
       </c>
       <c r="M31">
-        <v>0.17112602616748659</v>
+        <v>0.166459035138218</v>
       </c>
       <c r="N31">
-        <v>0.19473586071962309</v>
+        <v>0.1711260289055027</v>
       </c>
       <c r="O31">
-        <v>0.20692417867894031</v>
+        <v>0.1947358580012343</v>
       </c>
       <c r="P31">
-        <v>0.2525591361974372</v>
-      </c>
-    </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>46</v>
+        <v>0.2069241773418177</v>
+      </c>
+      <c r="Q31">
+        <v>0.2525591249755224</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,15)_</t>
+        </is>
       </c>
       <c r="B32">
-        <v>2.7504286522712751E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C32">
-        <v>4.5249321715328361E-2</v>
+        <v>0.02750428651681269</v>
       </c>
       <c r="D32">
-        <v>9.407355876725354E-2</v>
+        <v>0.0452493216865042</v>
       </c>
       <c r="E32">
-        <v>8.3712995103220278E-2</v>
+        <v>0.09407355786305205</v>
       </c>
       <c r="F32">
-        <v>0.10913991631748431</v>
+        <v>0.0837129946685311</v>
       </c>
       <c r="G32">
-        <v>0.1130555985882971</v>
+        <v>0.1091399155848612</v>
       </c>
       <c r="H32">
-        <v>0.12597374620357379</v>
+        <v>0.1130555976889865</v>
       </c>
       <c r="I32">
-        <v>0.15928702797543609</v>
+        <v>0.1259737459659431</v>
       </c>
       <c r="J32">
-        <v>0.142750650380053</v>
+        <v>0.1592870326103972</v>
       </c>
       <c r="K32">
-        <v>0.15547409185808689</v>
+        <v>0.1427506534704542</v>
       </c>
       <c r="L32">
-        <v>0.19739864934106111</v>
+        <v>0.1554741000144785</v>
       </c>
       <c r="M32">
-        <v>0.20706790573125339</v>
+        <v>0.1973986723337992</v>
       </c>
       <c r="N32">
-        <v>0.2619419584312368</v>
+        <v>0.2070679077185203</v>
       </c>
       <c r="O32">
-        <v>0.27850818600966382</v>
+        <v>0.2619419557535835</v>
       </c>
       <c r="P32">
-        <v>0.32373218508982182</v>
-      </c>
-    </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>47</v>
+        <v>0.2785081647882043</v>
+      </c>
+      <c r="Q32">
+        <v>0.3237321512176166</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,17)_</t>
+        </is>
       </c>
       <c r="B33">
-        <v>2.8041719537179599E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C33">
-        <v>4.5784718639044319E-2</v>
+        <v>0.02804171953130474</v>
       </c>
       <c r="D33">
-        <v>8.9482332911895668E-2</v>
+        <v>0.04578471861746169</v>
       </c>
       <c r="E33">
-        <v>8.5841737449277034E-2</v>
+        <v>0.08948233205536149</v>
       </c>
       <c r="F33">
-        <v>0.1080453372990391</v>
+        <v>0.08584173699843112</v>
       </c>
       <c r="G33">
-        <v>0.1117492006095795</v>
+        <v>0.1080453363450335</v>
       </c>
       <c r="H33">
-        <v>0.122111416860023</v>
+        <v>0.1117491996252186</v>
       </c>
       <c r="I33">
-        <v>0.1550870105893403</v>
+        <v>0.1221114165533541</v>
       </c>
       <c r="J33">
-        <v>0.14104670414309689</v>
+        <v>0.1550870142508775</v>
       </c>
       <c r="K33">
-        <v>0.1551337677533435</v>
+        <v>0.1410467058909103</v>
       </c>
       <c r="L33">
-        <v>0.18969551891405331</v>
+        <v>0.1551337742511001</v>
       </c>
       <c r="M33">
-        <v>0.19989214422166579</v>
+        <v>0.189695539740772</v>
       </c>
       <c r="N33">
-        <v>0.25354974980998829</v>
+        <v>0.1998921531103475</v>
       </c>
       <c r="O33">
-        <v>0.2641153013534554</v>
+        <v>0.2535497525919044</v>
       </c>
       <c r="P33">
-        <v>0.31023480850627222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>48</v>
+        <v>0.2641152948602061</v>
+      </c>
+      <c r="Q33">
+        <v>0.3102347711304948</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,19)_</t>
+        </is>
       </c>
       <c r="B34">
-        <v>2.8407194245906431E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C34">
-        <v>4.5511978076475217E-2</v>
+        <v>0.02840719423283733</v>
       </c>
       <c r="D34">
-        <v>8.724569702036955E-2</v>
+        <v>0.04551197803664775</v>
       </c>
       <c r="E34">
-        <v>8.782314712616146E-2</v>
+        <v>0.08724569614018252</v>
       </c>
       <c r="F34">
-        <v>0.1108525490217088</v>
+        <v>0.08782314654138501</v>
       </c>
       <c r="G34">
-        <v>0.11493066887088289</v>
+        <v>0.1108525479250133</v>
       </c>
       <c r="H34">
-        <v>0.1287074674766624</v>
+        <v>0.1149306682460621</v>
       </c>
       <c r="I34">
-        <v>0.15990116783641259</v>
+        <v>0.1287074666826971</v>
       </c>
       <c r="J34">
-        <v>0.14220865941341859</v>
+        <v>0.1599011710652674</v>
       </c>
       <c r="K34">
-        <v>0.15697352057333069</v>
+        <v>0.1422086617556835</v>
       </c>
       <c r="L34">
-        <v>0.18765030564860641</v>
+        <v>0.1569735291510411</v>
       </c>
       <c r="M34">
-        <v>0.19798990031512981</v>
+        <v>0.1876503263325699</v>
       </c>
       <c r="N34">
-        <v>0.2489750634121719</v>
+        <v>0.1979899042396726</v>
       </c>
       <c r="O34">
-        <v>0.25573942913989228</v>
+        <v>0.2489750641128917</v>
       </c>
       <c r="P34">
-        <v>0.29384010659319532</v>
-      </c>
-    </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>49</v>
+        <v>0.2557394386450556</v>
+      </c>
+      <c r="Q34">
+        <v>0.2938400597266182</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,21)_</t>
+        </is>
       </c>
       <c r="B35">
-        <v>2.7168574120662089E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C35">
-        <v>4.3121352039615091E-2</v>
+        <v>0.02716857411399498</v>
       </c>
       <c r="D35">
-        <v>8.412196443868325E-2</v>
+        <v>0.04312135199552325</v>
       </c>
       <c r="E35">
-        <v>8.2199797444934553E-2</v>
+        <v>0.08412196357864188</v>
       </c>
       <c r="F35">
-        <v>0.1050599065655634</v>
+        <v>0.08219979712495762</v>
       </c>
       <c r="G35">
-        <v>0.104190506225376</v>
+        <v>0.1050599055370237</v>
       </c>
       <c r="H35">
-        <v>0.1169836481086841</v>
+        <v>0.1041905053659902</v>
       </c>
       <c r="I35">
-        <v>0.14444620368144831</v>
+        <v>0.1169836471716877</v>
       </c>
       <c r="J35">
-        <v>0.13126372129387481</v>
+        <v>0.1444462070459859</v>
       </c>
       <c r="K35">
-        <v>0.14232979252192651</v>
+        <v>0.131263722499389</v>
       </c>
       <c r="L35">
-        <v>0.1691217010403773</v>
+        <v>0.1423297974550348</v>
       </c>
       <c r="M35">
-        <v>0.18000522273919761</v>
+        <v>0.169121713206813</v>
       </c>
       <c r="N35">
-        <v>0.23232390594850991</v>
+        <v>0.1800052271643005</v>
       </c>
       <c r="O35">
-        <v>0.24457732178705169</v>
+        <v>0.2323239056824317</v>
       </c>
       <c r="P35">
-        <v>0.28634598629109281</v>
-      </c>
-    </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>50</v>
+        <v>0.2445773249808424</v>
+      </c>
+      <c r="Q35">
+        <v>0.2863459384100984</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(0,3,31)_</t>
+        </is>
       </c>
       <c r="B36">
-        <v>2.666433162291271E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C36">
-        <v>4.4319894301593998E-2</v>
+        <v>0.02666433161085591</v>
       </c>
       <c r="D36">
-        <v>8.8800161069937267E-2</v>
+        <v>0.04431989425688854</v>
       </c>
       <c r="E36">
-        <v>8.2568029543353627E-2</v>
+        <v>0.08880016011011793</v>
       </c>
       <c r="F36">
-        <v>0.1073352207447297</v>
+        <v>0.0825680289995363</v>
       </c>
       <c r="G36">
-        <v>0.1094909714801028</v>
+        <v>0.1073352195960199</v>
       </c>
       <c r="H36">
-        <v>0.12115421657223931</v>
+        <v>0.1094909705306556</v>
       </c>
       <c r="I36">
-        <v>0.1472303658874872</v>
+        <v>0.121154215869166</v>
       </c>
       <c r="J36">
-        <v>0.13615139842391261</v>
+        <v>0.1472303659157648</v>
       </c>
       <c r="K36">
-        <v>0.14128413188742889</v>
+        <v>0.1361514003470095</v>
       </c>
       <c r="L36">
-        <v>0.1671772809020633</v>
+        <v>0.141284136142416</v>
       </c>
       <c r="M36">
-        <v>0.17381483822569899</v>
+        <v>0.1671772867531353</v>
       </c>
       <c r="N36">
-        <v>0.2027454475925409</v>
+        <v>0.1738148398586915</v>
       </c>
       <c r="O36">
-        <v>0.21752370083277811</v>
+        <v>0.2027453841205062</v>
       </c>
       <c r="P36">
-        <v>0.25803719496109678</v>
-      </c>
-    </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>51</v>
+        <v>0.2175236135141706</v>
+      </c>
+      <c r="Q36">
+        <v>0.2580371353150375</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,15)_</t>
+        </is>
       </c>
       <c r="B37">
-        <v>2.433597668854048E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C37">
-        <v>4.5665496466244071E-2</v>
+        <v>0.02433597669355214</v>
       </c>
       <c r="D37">
-        <v>9.8229804092664685E-2</v>
+        <v>0.04566549598501057</v>
       </c>
       <c r="E37">
-        <v>0.11782372505419279</v>
+        <v>0.09822980300868167</v>
       </c>
       <c r="F37">
-        <v>0.21000994372370141</v>
+        <v>0.1178237266425808</v>
       </c>
       <c r="G37">
-        <v>0.28292570341428802</v>
+        <v>0.2100099565307916</v>
       </c>
       <c r="H37">
-        <v>0.27156100120135579</v>
+        <v>0.2829257534302386</v>
       </c>
       <c r="I37">
-        <v>0.30567347385062998</v>
+        <v>0.2715610076220519</v>
       </c>
       <c r="J37">
-        <v>0.34176961066206402</v>
+        <v>0.3056734127131364</v>
       </c>
       <c r="K37">
-        <v>0.40459147755223218</v>
+        <v>0.3417695385137911</v>
       </c>
       <c r="L37">
-        <v>0.42096745089106441</v>
+        <v>0.4045913856722341</v>
       </c>
       <c r="M37">
-        <v>0.44935875298664368</v>
+        <v>0.4209673117151966</v>
       </c>
       <c r="N37">
-        <v>0.51091763684622193</v>
+        <v>0.4493586105584619</v>
       </c>
       <c r="O37">
-        <v>0.57342893410605877</v>
+        <v>0.510917491798409</v>
       </c>
       <c r="P37">
-        <v>0.60865567186718306</v>
-      </c>
-    </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>52</v>
+        <v>0.5734288256268981</v>
+      </c>
+      <c r="Q37">
+        <v>0.608655575130068</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,25)_</t>
+        </is>
       </c>
       <c r="B38">
-        <v>2.6731329636889511E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C38">
-        <v>4.2392453292670502E-2</v>
+        <v>0.02673132962328473</v>
       </c>
       <c r="D38">
-        <v>8.2347868617622888E-2</v>
+        <v>0.04239245278542036</v>
       </c>
       <c r="E38">
-        <v>9.4571239646587868E-2</v>
+        <v>0.08234786728202859</v>
       </c>
       <c r="F38">
-        <v>0.14934763057646899</v>
+        <v>0.09457123987363192</v>
       </c>
       <c r="G38">
-        <v>0.19539603279694939</v>
+        <v>0.1493476351309018</v>
       </c>
       <c r="H38">
-        <v>0.17622216648679229</v>
+        <v>0.1953960521981635</v>
       </c>
       <c r="I38">
-        <v>0.23174691773930309</v>
+        <v>0.1762221756958348</v>
       </c>
       <c r="J38">
-        <v>0.27845596726000332</v>
+        <v>0.2317469318318732</v>
       </c>
       <c r="K38">
-        <v>0.32835843293208911</v>
+        <v>0.2784559780467074</v>
       </c>
       <c r="L38">
-        <v>0.32788169026205038</v>
+        <v>0.3283584320354338</v>
       </c>
       <c r="M38">
-        <v>0.34176758313948158</v>
+        <v>0.327881684742525</v>
       </c>
       <c r="N38">
-        <v>0.37932496675126182</v>
+        <v>0.3417675748004755</v>
       </c>
       <c r="O38">
-        <v>0.42529573203889459</v>
+        <v>0.3793249260333155</v>
       </c>
       <c r="P38">
-        <v>0.42471491891699542</v>
-      </c>
-    </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>53</v>
+        <v>0.4252957460279296</v>
+      </c>
+      <c r="Q38">
+        <v>0.4247149544172049</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(1,3,31)_</t>
+        </is>
       </c>
       <c r="B39">
-        <v>2.822617041305386E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C39">
-        <v>4.3073624751423727E-2</v>
+        <v>0.02822617039691488</v>
       </c>
       <c r="D39">
-        <v>7.6907709423450932E-2</v>
+        <v>0.04307362425090655</v>
       </c>
       <c r="E39">
-        <v>8.5274536956821412E-2</v>
+        <v>0.07690770823530002</v>
       </c>
       <c r="F39">
-        <v>0.12590314171038169</v>
+        <v>0.08527453642372096</v>
       </c>
       <c r="G39">
-        <v>0.15969851948599961</v>
+        <v>0.1259031433994729</v>
       </c>
       <c r="H39">
-        <v>0.14161099970664401</v>
+        <v>0.1596985288957202</v>
       </c>
       <c r="I39">
-        <v>0.17564919034005019</v>
+        <v>0.1416110025056404</v>
       </c>
       <c r="J39">
-        <v>0.26067916475495567</v>
+        <v>0.1756491949349137</v>
       </c>
       <c r="K39">
-        <v>0.26913115976100122</v>
+        <v>0.2606791849361295</v>
       </c>
       <c r="L39">
-        <v>0.29341050170436378</v>
+        <v>0.2691311720168141</v>
       </c>
       <c r="M39">
-        <v>0.31833693732545648</v>
+        <v>0.2934105145457123</v>
       </c>
       <c r="N39">
-        <v>0.37590270254686903</v>
+        <v>0.3183369026369839</v>
       </c>
       <c r="O39">
-        <v>0.41435063148002771</v>
+        <v>0.3759025985523599</v>
       </c>
       <c r="P39">
-        <v>0.48023890000893482</v>
-      </c>
-    </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>54</v>
+        <v>0.4143504944058934</v>
+      </c>
+      <c r="Q39">
+        <v>0.4802388634980193</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>adj_ref2abs_red_c(1,1300,1)_snv_sder_c(2,3,21)_</t>
+        </is>
       </c>
       <c r="B40">
-        <v>2.7557925478080229E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C40">
-        <v>4.8788302908161052E-2</v>
+        <v>0.02755792557405501</v>
       </c>
       <c r="D40">
-        <v>6.1450503159405701E-2</v>
+        <v>0.04878830225543851</v>
       </c>
       <c r="E40">
-        <v>0.11084873482699741</v>
+        <v>0.0614505022213987</v>
       </c>
       <c r="F40">
-        <v>0.15078730808526891</v>
+        <v>0.1108487293499932</v>
       </c>
       <c r="G40">
-        <v>0.21595765447256679</v>
+        <v>0.1507873160402027</v>
       </c>
       <c r="H40">
-        <v>0.32852167103778951</v>
+        <v>0.2159576604642872</v>
       </c>
       <c r="I40">
-        <v>0.38233390014560309</v>
+        <v>0.3285217089360462</v>
       </c>
       <c r="J40">
-        <v>0.44610245387555902</v>
+        <v>0.3823340003717522</v>
       </c>
       <c r="K40">
-        <v>0.50394905499127818</v>
+        <v>0.4461024891007132</v>
       </c>
       <c r="L40">
-        <v>0.59556857442075473</v>
+        <v>0.5039490405910266</v>
       </c>
       <c r="M40">
-        <v>0.71858245933998011</v>
+        <v>0.5955686329774831</v>
       </c>
       <c r="N40">
-        <v>0.87996410471204367</v>
+        <v>0.7185826786728712</v>
       </c>
       <c r="O40">
-        <v>0.99632918534691639</v>
+        <v>0.8799646981637096</v>
       </c>
       <c r="P40">
-        <v>1.0404115957595541</v>
-      </c>
-    </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>55</v>
+        <v>0.9963297667377533</v>
+      </c>
+      <c r="Q40">
+        <v>1.04041204828626</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(1,3,5)_</t>
+        </is>
       </c>
       <c r="B41">
-        <v>4.2948083670724557E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C41">
-        <v>6.3524369480308596E-2</v>
+        <v>0.04294808370593645</v>
       </c>
       <c r="D41">
-        <v>0.14501881335244929</v>
+        <v>0.06352436850306631</v>
       </c>
       <c r="E41">
-        <v>0.26553021143556099</v>
+        <v>0.1450188119629703</v>
       </c>
       <c r="F41">
-        <v>0.37584796846632612</v>
+        <v>0.2655302008045972</v>
       </c>
       <c r="G41">
-        <v>0.41289532840781229</v>
+        <v>0.3758479390998244</v>
       </c>
       <c r="H41">
-        <v>0.46694811326055657</v>
+        <v>0.4128953094821287</v>
       </c>
       <c r="I41">
-        <v>0.48776223752542208</v>
+        <v>0.4669481182830627</v>
       </c>
       <c r="J41">
-        <v>0.50917371013470414</v>
+        <v>0.4877622634199364</v>
       </c>
       <c r="K41">
-        <v>0.54076857116934596</v>
+        <v>0.5091737239801045</v>
       </c>
       <c r="L41">
-        <v>0.59054927082588327</v>
+        <v>0.5407685583994468</v>
       </c>
       <c r="M41">
-        <v>0.68378369864211352</v>
+        <v>0.5905492263175673</v>
       </c>
       <c r="N41">
-        <v>0.73571348582947094</v>
+        <v>0.6837836293665931</v>
       </c>
       <c r="O41">
-        <v>0.7734762015279909</v>
+        <v>0.7357133945156358</v>
       </c>
       <c r="P41">
-        <v>0.78486421587048127</v>
-      </c>
-    </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" t="s">
-        <v>56</v>
+        <v>0.7734760735467956</v>
+      </c>
+      <c r="Q41">
+        <v>0.7848640777536156</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>adj_snv_sder_c(2,3,15)_</t>
+        </is>
       </c>
       <c r="B42">
-        <v>5.0610996410996811E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C42">
-        <v>4.9652744075355359E-2</v>
+        <v>0.05061099605863495</v>
       </c>
       <c r="D42">
-        <v>0.11172834959077731</v>
+        <v>0.04965274407531617</v>
       </c>
       <c r="E42">
-        <v>0.2241597969625313</v>
+        <v>0.1117283489899722</v>
       </c>
       <c r="F42">
-        <v>0.2350201190264527</v>
+        <v>0.2241597930016773</v>
       </c>
       <c r="G42">
-        <v>0.27460026452173009</v>
+        <v>0.2350201122057721</v>
       </c>
       <c r="H42">
-        <v>0.29975754083076162</v>
+        <v>0.274600262674576</v>
       </c>
       <c r="I42">
-        <v>0.32761326656952983</v>
+        <v>0.2997575439660451</v>
       </c>
       <c r="J42">
-        <v>0.47626696806117891</v>
+        <v>0.3276132648487888</v>
       </c>
       <c r="K42">
-        <v>0.57949607019498606</v>
+        <v>0.4762669606649163</v>
       </c>
       <c r="L42">
-        <v>0.66258855631554237</v>
+        <v>0.5794960572560152</v>
       </c>
       <c r="M42">
-        <v>0.69335811467738806</v>
+        <v>0.6625884947784053</v>
       </c>
       <c r="N42">
-        <v>0.72003983253363568</v>
+        <v>0.6933580217552823</v>
       </c>
       <c r="O42">
-        <v>0.72118791165257234</v>
+        <v>0.7200397568034306</v>
       </c>
       <c r="P42">
-        <v>0.71765424066952577</v>
-      </c>
-    </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A43" t="s">
-        <v>57</v>
+        <v>0.7211878064672539</v>
+      </c>
+      <c r="Q42">
+        <v>0.717654073693639</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>snv_sder_c(1,3,9)_red_c(10,10,1)_</t>
+        </is>
       </c>
       <c r="B43">
-        <v>2.9604078281788019E-2</v>
+        <v>0.018778932657874</v>
       </c>
       <c r="C43">
-        <v>9.5842294690364649E-2</v>
+        <v>0.02960407822249789</v>
       </c>
       <c r="D43">
-        <v>0.13352344123521109</v>
+        <v>0.09584229502424285</v>
       </c>
       <c r="E43">
-        <v>0.20297036902505999</v>
+        <v>0.1335234415046188</v>
       </c>
       <c r="F43">
-        <v>0.30525102929819808</v>
+        <v>0.2029703707975136</v>
       </c>
       <c r="G43">
-        <v>0.35264806264180898</v>
+        <v>0.3052510307210335</v>
       </c>
       <c r="H43">
-        <v>0.35840352200177789</v>
+        <v>0.3526480658679924</v>
       </c>
       <c r="I43">
-        <v>0.37291111177949821</v>
+        <v>0.3584035245907697</v>
       </c>
       <c r="J43">
-        <v>0.40895790952805888</v>
+        <v>0.3729111104582756</v>
       </c>
       <c r="K43">
-        <v>0.49621382285396731</v>
+        <v>0.4089579031478506</v>
       </c>
       <c r="L43">
-        <v>0.5463636630445915</v>
+        <v>0.4962138174836333</v>
       </c>
       <c r="M43">
-        <v>0.59032380253721839</v>
+        <v>0.5463636602710891</v>
       </c>
       <c r="N43">
-        <v>0.60939340873870385</v>
+        <v>0.5903237944428253</v>
       </c>
       <c r="O43">
-        <v>0.62777011781836056</v>
+        <v>0.6093933850077298</v>
       </c>
       <c r="P43">
-        <v>0.66654070451182579</v>
+        <v>0.627770068943489</v>
+      </c>
+      <c r="Q43">
+        <v>0.6665405971920398</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B2:P43">
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
-      <formula>0.2</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <formula>0.2</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>